--- a/hall/resources/sample/runninglight.xlsx
+++ b/hall/resources/sample/runninglight.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -296,6 +301,18 @@
   </si>
   <si>
     <t>30_40_50_78</t>
+  </si>
+  <si>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
   </si>
 </sst>
 </file>
@@ -308,7 +325,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,12 +348,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -810,142 +821,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -960,10 +968,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1291,7 +1299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.75" style="1" customWidth="1"/>
@@ -1306,31 +1314,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1347,16 +1355,16 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1387,40 +1395,35 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1">
         <f>B5*10+E5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>100100</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>100100026</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1428,29 +1431,26 @@
         <f t="shared" ref="A6:A37" si="0">B6*10+E6</f>
         <v>1001002</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>100100</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>100100026</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1458,29 +1458,26 @@
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>100100</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>100100026</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1488,22 +1485,22 @@
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>100300</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>100300001</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="1">
@@ -1518,22 +1515,22 @@
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>100300</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>100300001</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="1">
@@ -1548,22 +1545,22 @@
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>100300</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>100300001</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="1">
@@ -1578,22 +1575,22 @@
         <f t="shared" si="0"/>
         <v>1007001</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>100700</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>100700001</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="1">
@@ -1608,22 +1605,22 @@
         <f t="shared" si="0"/>
         <v>1007002</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>100700</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>100700001</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="1">
@@ -1638,22 +1635,22 @@
         <f t="shared" si="0"/>
         <v>1007003</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>100700</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>100700001</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="1">
@@ -1668,22 +1665,22 @@
         <f t="shared" si="0"/>
         <v>1012001</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>101200</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>101200001</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="1">
@@ -1698,22 +1695,22 @@
         <f t="shared" si="0"/>
         <v>1012002</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>101200</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>101200001</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="1">
@@ -1728,22 +1725,22 @@
         <f t="shared" si="0"/>
         <v>1012003</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>101200</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>101200001</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="1">
@@ -1758,29 +1755,26 @@
         <f t="shared" si="0"/>
         <v>1014001</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>101400</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>101400001</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1788,29 +1782,26 @@
         <f t="shared" si="0"/>
         <v>1014002</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>101400</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>101400001</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
-      </c>
-      <c r="I18" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1818,29 +1809,26 @@
         <f t="shared" si="0"/>
         <v>1014003</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>101400</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>101400001</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
-      </c>
-      <c r="I19" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1848,29 +1836,26 @@
         <f t="shared" si="0"/>
         <v>1017001</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>101700</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>101700001</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
-      </c>
-      <c r="I20" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1878,29 +1863,26 @@
         <f t="shared" si="0"/>
         <v>1017002</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>101700</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>101700001</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
-      </c>
-      <c r="I21" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1908,29 +1890,26 @@
         <f t="shared" si="0"/>
         <v>1017003</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>101700</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>101700001</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
-      </c>
-      <c r="I22" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1938,22 +1917,22 @@
         <f t="shared" si="0"/>
         <v>1021001</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>102100</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>102100001</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="1">
@@ -1968,22 +1947,22 @@
         <f t="shared" si="0"/>
         <v>1021002</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>102100</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>102100001</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="1">
@@ -1998,22 +1977,22 @@
         <f t="shared" si="0"/>
         <v>1021003</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>102100</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>102100001</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="1">
@@ -2028,22 +2007,22 @@
         <f t="shared" si="0"/>
         <v>1022001</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>102200</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <v>102200001</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H26" s="1">
@@ -2058,22 +2037,22 @@
         <f t="shared" si="0"/>
         <v>1022002</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="3">
         <v>102200</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>102200001</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="1">
@@ -2088,22 +2067,22 @@
         <f t="shared" si="0"/>
         <v>1022003</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="3">
         <v>102200</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <v>102200001</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="1">
@@ -2118,29 +2097,26 @@
         <f t="shared" si="0"/>
         <v>1024001</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="3">
         <v>102400</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>102400026</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
-      </c>
-      <c r="I29" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2148,29 +2124,26 @@
         <f t="shared" si="0"/>
         <v>1024002</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="3">
         <v>102400</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <v>102400026</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
-      </c>
-      <c r="I30" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2178,29 +2151,26 @@
         <f t="shared" si="0"/>
         <v>1024003</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="3">
         <v>102400</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>102400026</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
-      </c>
-      <c r="I31" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2208,22 +2178,22 @@
         <f t="shared" si="0"/>
         <v>1018001</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="3">
         <v>101800</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="5">
         <v>101800001</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="1">
@@ -2238,22 +2208,22 @@
         <f t="shared" si="0"/>
         <v>1018002</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="3">
         <v>101800</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>101800001</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="1">
@@ -2268,22 +2238,22 @@
         <f t="shared" si="0"/>
         <v>1018003</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="3">
         <v>101800</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <v>101800001</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="1">
@@ -2298,22 +2268,22 @@
         <f t="shared" si="0"/>
         <v>1025001</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="3">
         <v>102500</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="5">
         <v>102500001</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H35" s="1">
@@ -2328,22 +2298,22 @@
         <f t="shared" si="0"/>
         <v>1025002</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="3">
         <v>102500</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="5">
         <v>102500001</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H36" s="1">
@@ -2358,22 +2328,22 @@
         <f t="shared" si="0"/>
         <v>1025003</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="3">
         <v>102500</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="5">
         <v>102500001</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H37" s="1">
@@ -2388,29 +2358,26 @@
         <f t="shared" ref="A38:A69" si="1">B38*10+E38</f>
         <v>1023001</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="3">
         <v>102300</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="5">
         <v>102300001</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
-      </c>
-      <c r="I38" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2418,29 +2385,26 @@
         <f t="shared" si="1"/>
         <v>1023002</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="3">
         <v>102300</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="5">
         <v>102300001</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2448,29 +2412,26 @@
         <f t="shared" si="1"/>
         <v>1023003</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="3">
         <v>102300</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="5">
         <v>102300001</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
-      </c>
-      <c r="I40" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2478,29 +2439,26 @@
         <f t="shared" si="1"/>
         <v>1034001</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="3">
         <v>103400</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="5">
         <v>103000001</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
-      </c>
-      <c r="I41" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2508,29 +2466,26 @@
         <f t="shared" si="1"/>
         <v>1034002</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="3">
         <v>103400</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="5">
         <v>103000001</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2538,29 +2493,26 @@
         <f t="shared" si="1"/>
         <v>1034003</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="3">
         <v>103400</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="5">
         <v>103000001</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
-      </c>
-      <c r="I43" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2568,29 +2520,26 @@
         <f t="shared" si="1"/>
         <v>1035001</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="3">
         <v>103500</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="5">
         <v>102900001</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
-      </c>
-      <c r="I44" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2598,29 +2547,26 @@
         <f t="shared" si="1"/>
         <v>1035002</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="3">
         <v>103500</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="5">
         <v>102900001</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
-      </c>
-      <c r="I45" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2628,29 +2574,26 @@
         <f t="shared" si="1"/>
         <v>1035003</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="3">
         <v>103500</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="5">
         <v>102900001</v>
       </c>
       <c r="E46" s="1">
         <v>3</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
-      </c>
-      <c r="I46" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2658,29 +2601,26 @@
         <f t="shared" si="1"/>
         <v>1035011</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="3">
         <v>103501</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="5">
         <v>103501001</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
-      </c>
-      <c r="I47" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2688,29 +2628,26 @@
         <f t="shared" si="1"/>
         <v>1035012</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="3">
         <v>103501</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="5">
         <v>103501001</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
-      </c>
-      <c r="I48" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2718,29 +2655,26 @@
         <f t="shared" si="1"/>
         <v>1035013</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="3">
         <v>103501</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="5">
         <v>103501001</v>
       </c>
       <c r="E49" s="1">
         <v>3</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2748,29 +2682,26 @@
         <f t="shared" si="1"/>
         <v>1036001</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="3">
         <v>103600</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="5">
         <v>103600001</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
-      </c>
-      <c r="I50" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2778,29 +2709,26 @@
         <f t="shared" si="1"/>
         <v>1036002</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="3">
         <v>103600</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="5">
         <v>103600001</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
-      </c>
-      <c r="I51" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2808,29 +2736,26 @@
         <f t="shared" si="1"/>
         <v>1036003</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="3">
         <v>103600</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="5">
         <v>103600001</v>
       </c>
       <c r="E52" s="1">
         <v>3</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
-      </c>
-      <c r="I52" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2838,22 +2763,22 @@
         <f t="shared" si="1"/>
         <v>1020001</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="3">
         <v>102000</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="5">
         <v>102000001</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H53" s="1">
@@ -2868,22 +2793,22 @@
         <f t="shared" si="1"/>
         <v>1020002</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="3">
         <v>102000</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="5">
         <v>102000001</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H54" s="1">
@@ -2898,22 +2823,22 @@
         <f t="shared" si="1"/>
         <v>1020003</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="3">
         <v>102000</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="5">
         <v>102000001</v>
       </c>
       <c r="E55" s="1">
         <v>3</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H55" s="1">
@@ -2928,29 +2853,26 @@
         <f t="shared" si="1"/>
         <v>1034011</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="3">
         <v>103401</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="5">
         <v>103400001</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
-      </c>
-      <c r="I56" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2958,29 +2880,26 @@
         <f t="shared" si="1"/>
         <v>1034012</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="3">
         <v>103401</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="5">
         <v>103400001</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
-      </c>
-      <c r="I57" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2988,29 +2907,26 @@
         <f t="shared" si="1"/>
         <v>1034013</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="3">
         <v>103401</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="5">
         <v>103400001</v>
       </c>
       <c r="E58" s="1">
         <v>3</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3018,29 +2934,26 @@
         <f t="shared" si="1"/>
         <v>1038001</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="3">
         <v>103800</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="5">
         <v>103800001</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
-      </c>
-      <c r="I59" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3048,29 +2961,26 @@
         <f t="shared" si="1"/>
         <v>1038002</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="3">
         <v>103800</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="5">
         <v>103800001</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
-      </c>
-      <c r="I60" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3078,29 +2988,26 @@
         <f t="shared" si="1"/>
         <v>1038003</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="3">
         <v>103800</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="5">
         <v>103800001</v>
       </c>
       <c r="E61" s="1">
         <v>3</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
-      </c>
-      <c r="I61" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -3108,29 +3015,26 @@
         <f t="shared" si="1"/>
         <v>1040001</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="3">
         <v>104000</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="5">
         <v>104000001</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
-      </c>
-      <c r="I62" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3138,29 +3042,26 @@
         <f t="shared" si="1"/>
         <v>1040002</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="3">
         <v>104000</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="5">
         <v>104000001</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
-      </c>
-      <c r="I63" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3168,43 +3069,40 @@
         <f t="shared" si="1"/>
         <v>1040003</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="3">
         <v>104000</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="5">
         <v>104000001</v>
       </c>
       <c r="E64" s="1">
         <v>3</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
       </c>
-      <c r="I64" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <f t="shared" si="1"/>
         <v>2001001</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="7">
         <v>200100</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="9">
         <v>200100038</v>
       </c>
       <c r="E65" s="1">
@@ -3213,28 +3111,25 @@
       <c r="F65" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="10" t="s">
         <v>62</v>
       </c>
       <c r="H65" s="1">
         <v>300</v>
       </c>
-      <c r="I65" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <f t="shared" si="1"/>
         <v>2001002</v>
       </c>
-      <c r="B66" s="8">
+      <c r="B66" s="7">
         <v>200100</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="9">
         <v>200100038</v>
       </c>
       <c r="E66" s="1">
@@ -3243,28 +3138,25 @@
       <c r="F66" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="10" t="s">
         <v>62</v>
       </c>
       <c r="H66" s="1">
         <v>300</v>
       </c>
-      <c r="I66" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <f t="shared" si="1"/>
         <v>2001003</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="7">
         <v>200100</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D67" s="10">
+      <c r="D67" s="9">
         <v>200100038</v>
       </c>
       <c r="E67" s="1">
@@ -3273,28 +3165,25 @@
       <c r="F67" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="10" t="s">
         <v>62</v>
       </c>
       <c r="H67" s="1">
         <v>300</v>
       </c>
-      <c r="I67" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="1">
         <f t="shared" si="1"/>
         <v>2001011</v>
       </c>
-      <c r="B68" s="8">
+      <c r="B68" s="7">
         <v>200101</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D68" s="10">
+      <c r="D68" s="9">
         <v>200101001</v>
       </c>
       <c r="E68" s="1">
@@ -3303,28 +3192,25 @@
       <c r="F68" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G68" s="10">
         <v>8</v>
       </c>
       <c r="H68" s="1">
         <v>300</v>
       </c>
-      <c r="I68" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <f t="shared" si="1"/>
         <v>2001012</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="7">
         <v>200101</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="9">
         <v>200101001</v>
       </c>
       <c r="E69" s="1">
@@ -3333,28 +3219,25 @@
       <c r="F69" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G69" s="11">
+      <c r="G69" s="10">
         <v>8</v>
       </c>
       <c r="H69" s="1">
         <v>300</v>
       </c>
-      <c r="I69" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <f t="shared" ref="A70:A101" si="2">B70*10+E70</f>
+        <f t="shared" ref="A70:A103" si="2">B70*10+E70</f>
         <v>2001013</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="7">
         <v>200101</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="9">
         <v>200101001</v>
       </c>
       <c r="E70" s="1">
@@ -3363,28 +3246,25 @@
       <c r="F70" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G70" s="10">
         <v>8</v>
       </c>
       <c r="H70" s="1">
         <v>300</v>
       </c>
-      <c r="I70" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <f t="shared" si="2"/>
         <v>2003001</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="7">
         <v>200300</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="9">
         <v>200300001</v>
       </c>
       <c r="E71" s="1">
@@ -3393,28 +3273,25 @@
       <c r="F71" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G71" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H71" s="1">
         <v>300</v>
       </c>
-      <c r="I71" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <f t="shared" si="2"/>
         <v>2003002</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="7">
         <v>200300</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D72" s="10">
+      <c r="D72" s="9">
         <v>200300001</v>
       </c>
       <c r="E72" s="1">
@@ -3423,28 +3300,25 @@
       <c r="F72" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G72" s="11" t="s">
+      <c r="G72" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H72" s="1">
         <v>300</v>
       </c>
-      <c r="I72" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <f t="shared" si="2"/>
         <v>2003003</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="7">
         <v>200300</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="9">
         <v>200300001</v>
       </c>
       <c r="E73" s="1">
@@ -3453,28 +3327,25 @@
       <c r="F73" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="G73" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H73" s="1">
         <v>300</v>
       </c>
-      <c r="I73" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <f t="shared" si="2"/>
         <v>2004001</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="7">
         <v>200400</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D74" s="10">
+      <c r="D74" s="9">
         <v>200400009</v>
       </c>
       <c r="E74" s="1">
@@ -3483,28 +3354,25 @@
       <c r="F74" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="10" t="s">
         <v>68</v>
       </c>
       <c r="H74" s="1">
         <v>300</v>
       </c>
-      <c r="I74" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
         <f t="shared" si="2"/>
         <v>2004002</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="7">
         <v>200400</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D75" s="10">
+      <c r="D75" s="9">
         <v>200400009</v>
       </c>
       <c r="E75" s="1">
@@ -3513,28 +3381,25 @@
       <c r="F75" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="10" t="s">
         <v>68</v>
       </c>
       <c r="H75" s="1">
         <v>300</v>
       </c>
-      <c r="I75" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="1">
         <f t="shared" si="2"/>
         <v>2004003</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="7">
         <v>200400</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D76" s="10">
+      <c r="D76" s="9">
         <v>200400009</v>
       </c>
       <c r="E76" s="1">
@@ -3543,28 +3408,25 @@
       <c r="F76" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="10" t="s">
         <v>68</v>
       </c>
       <c r="H76" s="1">
         <v>300</v>
       </c>
-      <c r="I76" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <f t="shared" si="2"/>
         <v>2005001</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="7">
         <v>200500</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D77" s="10">
+      <c r="D77" s="9">
         <v>200500025</v>
       </c>
       <c r="E77" s="1">
@@ -3573,28 +3435,25 @@
       <c r="F77" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="G77" s="10" t="s">
         <v>70</v>
       </c>
       <c r="H77" s="1">
         <v>300</v>
       </c>
-      <c r="I77" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <f t="shared" si="2"/>
         <v>2005002</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="7">
         <v>200500</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D78" s="10">
+      <c r="D78" s="9">
         <v>200500025</v>
       </c>
       <c r="E78" s="1">
@@ -3603,28 +3462,25 @@
       <c r="F78" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G78" s="11" t="s">
+      <c r="G78" s="10" t="s">
         <v>70</v>
       </c>
       <c r="H78" s="1">
         <v>300</v>
       </c>
-      <c r="I78" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <f t="shared" si="2"/>
         <v>2005003</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="7">
         <v>200500</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D79" s="10">
+      <c r="D79" s="9">
         <v>200500025</v>
       </c>
       <c r="E79" s="1">
@@ -3633,28 +3489,25 @@
       <c r="F79" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G79" s="10" t="s">
         <v>70</v>
       </c>
       <c r="H79" s="1">
         <v>300</v>
       </c>
-      <c r="I79" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <f t="shared" si="2"/>
         <v>2006001</v>
       </c>
-      <c r="B80" s="8">
+      <c r="B80" s="7">
         <v>200600</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="C80" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D80" s="10">
+      <c r="D80" s="9">
         <v>200600001</v>
       </c>
       <c r="E80" s="1">
@@ -3663,28 +3516,25 @@
       <c r="F80" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="10" t="s">
         <v>72</v>
       </c>
       <c r="H80" s="1">
         <v>300</v>
       </c>
-      <c r="I80" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <f t="shared" si="2"/>
         <v>2006002</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B81" s="7">
         <v>200600</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D81" s="10">
+      <c r="D81" s="9">
         <v>200600001</v>
       </c>
       <c r="E81" s="1">
@@ -3693,28 +3543,25 @@
       <c r="F81" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G81" s="11" t="s">
+      <c r="G81" s="10" t="s">
         <v>72</v>
       </c>
       <c r="H81" s="1">
         <v>300</v>
       </c>
-      <c r="I81" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <f t="shared" si="2"/>
         <v>2006003</v>
       </c>
-      <c r="B82" s="8">
+      <c r="B82" s="7">
         <v>200600</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D82" s="10">
+      <c r="D82" s="9">
         <v>200600001</v>
       </c>
       <c r="E82" s="1">
@@ -3723,28 +3570,25 @@
       <c r="F82" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G82" s="11" t="s">
+      <c r="G82" s="10" t="s">
         <v>72</v>
       </c>
       <c r="H82" s="1">
         <v>300</v>
       </c>
-      <c r="I82" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <f t="shared" si="2"/>
         <v>2007001</v>
       </c>
-      <c r="B83" s="8">
+      <c r="B83" s="7">
         <v>200700</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="C83" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D83" s="10">
+      <c r="D83" s="9">
         <v>200700001</v>
       </c>
       <c r="E83" s="1">
@@ -3753,28 +3597,25 @@
       <c r="F83" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G83" s="11" t="s">
+      <c r="G83" s="10" t="s">
         <v>74</v>
       </c>
       <c r="H83" s="1">
         <v>300</v>
       </c>
-      <c r="I83" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="1">
         <f t="shared" si="2"/>
         <v>2007002</v>
       </c>
-      <c r="B84" s="8">
+      <c r="B84" s="7">
         <v>200700</v>
       </c>
-      <c r="C84" s="9" t="s">
+      <c r="C84" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D84" s="10">
+      <c r="D84" s="9">
         <v>200700001</v>
       </c>
       <c r="E84" s="1">
@@ -3783,28 +3624,25 @@
       <c r="F84" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G84" s="11" t="s">
+      <c r="G84" s="10" t="s">
         <v>74</v>
       </c>
       <c r="H84" s="1">
         <v>300</v>
       </c>
-      <c r="I84" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="1">
         <f t="shared" si="2"/>
         <v>2007003</v>
       </c>
-      <c r="B85" s="8">
+      <c r="B85" s="7">
         <v>200700</v>
       </c>
-      <c r="C85" s="9" t="s">
+      <c r="C85" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D85" s="10">
+      <c r="D85" s="9">
         <v>200700001</v>
       </c>
       <c r="E85" s="1">
@@ -3813,28 +3651,25 @@
       <c r="F85" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="10" t="s">
         <v>74</v>
       </c>
       <c r="H85" s="1">
         <v>300</v>
       </c>
-      <c r="I85" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <f t="shared" si="2"/>
         <v>2008001</v>
       </c>
-      <c r="B86" s="8">
+      <c r="B86" s="7">
         <v>200800</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="C86" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D86" s="10">
+      <c r="D86" s="9">
         <v>200800001</v>
       </c>
       <c r="E86" s="1">
@@ -3843,28 +3678,25 @@
       <c r="F86" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G86" s="11">
+      <c r="G86" s="10">
         <v>1</v>
       </c>
       <c r="H86" s="1">
         <v>300</v>
       </c>
-      <c r="I86" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="1">
         <f t="shared" si="2"/>
         <v>2008002</v>
       </c>
-      <c r="B87" s="8">
+      <c r="B87" s="7">
         <v>200800</v>
       </c>
-      <c r="C87" s="9" t="s">
+      <c r="C87" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D87" s="10">
+      <c r="D87" s="9">
         <v>200800001</v>
       </c>
       <c r="E87" s="1">
@@ -3873,28 +3705,25 @@
       <c r="F87" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G87" s="11">
+      <c r="G87" s="10">
         <v>1</v>
       </c>
       <c r="H87" s="1">
         <v>300</v>
       </c>
-      <c r="I87" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <f t="shared" si="2"/>
         <v>2008003</v>
       </c>
-      <c r="B88" s="8">
+      <c r="B88" s="7">
         <v>200800</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D88" s="10">
+      <c r="D88" s="9">
         <v>200800001</v>
       </c>
       <c r="E88" s="1">
@@ -3903,28 +3732,25 @@
       <c r="F88" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G88" s="11">
+      <c r="G88" s="10">
         <v>1</v>
       </c>
       <c r="H88" s="1">
         <v>300</v>
       </c>
-      <c r="I88" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <f t="shared" si="2"/>
         <v>2009001</v>
       </c>
-      <c r="B89" s="8">
+      <c r="B89" s="7">
         <v>200900</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C89" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D89" s="10">
+      <c r="D89" s="9">
         <v>200900001</v>
       </c>
       <c r="E89" s="1">
@@ -3933,28 +3759,25 @@
       <c r="F89" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G89" s="11" t="s">
+      <c r="G89" s="10" t="s">
         <v>77</v>
       </c>
       <c r="H89" s="1">
         <v>300</v>
       </c>
-      <c r="I89" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <f t="shared" si="2"/>
         <v>2009002</v>
       </c>
-      <c r="B90" s="8">
+      <c r="B90" s="7">
         <v>200900</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D90" s="10">
+      <c r="D90" s="9">
         <v>200900001</v>
       </c>
       <c r="E90" s="1">
@@ -3963,28 +3786,25 @@
       <c r="F90" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G90" s="11" t="s">
+      <c r="G90" s="10" t="s">
         <v>77</v>
       </c>
       <c r="H90" s="1">
         <v>300</v>
       </c>
-      <c r="I90" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="1">
         <f t="shared" si="2"/>
         <v>2009003</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="7">
         <v>200900</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C91" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D91" s="10">
+      <c r="D91" s="9">
         <v>200900001</v>
       </c>
       <c r="E91" s="1">
@@ -3993,28 +3813,25 @@
       <c r="F91" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G91" s="11" t="s">
+      <c r="G91" s="10" t="s">
         <v>77</v>
       </c>
       <c r="H91" s="1">
         <v>300</v>
       </c>
-      <c r="I91" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <f t="shared" si="2"/>
         <v>2012001</v>
       </c>
-      <c r="B92" s="8">
+      <c r="B92" s="7">
         <v>201200</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D92" s="10">
+      <c r="D92" s="9">
         <v>201200001</v>
       </c>
       <c r="E92" s="1">
@@ -4023,28 +3840,25 @@
       <c r="F92" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G92" s="11" t="s">
+      <c r="G92" s="10" t="s">
         <v>79</v>
       </c>
       <c r="H92" s="1">
         <v>300</v>
       </c>
-      <c r="I92" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <f t="shared" si="2"/>
         <v>2012002</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="7">
         <v>201200</v>
       </c>
-      <c r="C93" s="9" t="s">
+      <c r="C93" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D93" s="10">
+      <c r="D93" s="9">
         <v>201200001</v>
       </c>
       <c r="E93" s="1">
@@ -4053,28 +3867,25 @@
       <c r="F93" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G93" s="11" t="s">
+      <c r="G93" s="10" t="s">
         <v>79</v>
       </c>
       <c r="H93" s="1">
         <v>300</v>
       </c>
-      <c r="I93" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="1">
         <f t="shared" si="2"/>
         <v>2012003</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="7">
         <v>201200</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="C94" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D94" s="10">
+      <c r="D94" s="9">
         <v>201200001</v>
       </c>
       <c r="E94" s="1">
@@ -4083,28 +3894,25 @@
       <c r="F94" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G94" s="11" t="s">
+      <c r="G94" s="10" t="s">
         <v>79</v>
       </c>
       <c r="H94" s="1">
         <v>300</v>
       </c>
-      <c r="I94" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9">
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <f t="shared" si="2"/>
         <v>3001001</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="7">
         <v>300100</v>
       </c>
-      <c r="C95" s="9" t="s">
+      <c r="C95" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D95" s="10">
+      <c r="D95" s="9">
         <v>300100001</v>
       </c>
       <c r="E95" s="1">
@@ -4113,28 +3921,25 @@
       <c r="F95" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G95" s="11" t="s">
+      <c r="G95" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H95" s="1">
         <v>300</v>
       </c>
-      <c r="I95" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9">
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <f t="shared" si="2"/>
         <v>3001002</v>
       </c>
-      <c r="B96" s="8">
+      <c r="B96" s="7">
         <v>300100</v>
       </c>
-      <c r="C96" s="9" t="s">
+      <c r="C96" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D96" s="10">
+      <c r="D96" s="9">
         <v>300100001</v>
       </c>
       <c r="E96" s="1">
@@ -4143,14 +3948,11 @@
       <c r="F96" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G96" s="11" t="s">
+      <c r="G96" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H96" s="1">
         <v>300</v>
-      </c>
-      <c r="I96" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -4158,13 +3960,13 @@
         <f t="shared" si="2"/>
         <v>3001003</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="7">
         <v>300100</v>
       </c>
-      <c r="C97" s="9" t="s">
+      <c r="C97" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D97" s="10">
+      <c r="D97" s="9">
         <v>300100001</v>
       </c>
       <c r="E97" s="1">
@@ -4173,14 +3975,11 @@
       <c r="F97" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G97" s="11" t="s">
+      <c r="G97" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H97" s="1">
         <v>300</v>
-      </c>
-      <c r="I97" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4188,13 +3987,13 @@
         <f t="shared" si="2"/>
         <v>3002001</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="7">
         <v>300200</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C98" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D98" s="10">
+      <c r="D98" s="9">
         <v>300200006</v>
       </c>
       <c r="E98" s="1">
@@ -4203,14 +4002,11 @@
       <c r="F98" s="1">
         <v>1000</v>
       </c>
-      <c r="G98" s="11" t="s">
+      <c r="G98" s="10" t="s">
         <v>86</v>
       </c>
       <c r="H98" s="1">
         <v>300</v>
-      </c>
-      <c r="I98" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -4218,13 +4014,13 @@
         <f t="shared" si="2"/>
         <v>3002002</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="7">
         <v>300200</v>
       </c>
-      <c r="C99" s="9" t="s">
+      <c r="C99" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D99" s="10">
+      <c r="D99" s="9">
         <v>300200006</v>
       </c>
       <c r="E99" s="1">
@@ -4233,14 +4029,11 @@
       <c r="F99" s="1">
         <v>10000</v>
       </c>
-      <c r="G99" s="11" t="s">
+      <c r="G99" s="10" t="s">
         <v>86</v>
       </c>
       <c r="H99" s="1">
         <v>300</v>
-      </c>
-      <c r="I99" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -4248,13 +4041,13 @@
         <f t="shared" si="2"/>
         <v>3002003</v>
       </c>
-      <c r="B100" s="8">
+      <c r="B100" s="7">
         <v>300200</v>
       </c>
-      <c r="C100" s="9" t="s">
+      <c r="C100" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D100" s="10">
+      <c r="D100" s="9">
         <v>300200006</v>
       </c>
       <c r="E100" s="1">
@@ -4263,14 +4056,11 @@
       <c r="F100" s="1">
         <v>100000</v>
       </c>
-      <c r="G100" s="11" t="s">
+      <c r="G100" s="10" t="s">
         <v>86</v>
       </c>
       <c r="H100" s="1">
         <v>300</v>
-      </c>
-      <c r="I100" s="1">
-        <v>17001</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -4278,13 +4068,13 @@
         <f t="shared" si="2"/>
         <v>3004001</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="7">
         <v>300400</v>
       </c>
-      <c r="C101" s="9" t="s">
+      <c r="C101" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D101" s="10">
+      <c r="D101" s="9">
         <v>300400023</v>
       </c>
       <c r="E101" s="1">
@@ -4293,28 +4083,25 @@
       <c r="F101" s="1">
         <v>100</v>
       </c>
-      <c r="G101" s="11" t="s">
+      <c r="G101" s="10" t="s">
         <v>88</v>
       </c>
       <c r="H101" s="1">
         <v>300</v>
       </c>
-      <c r="I101" s="1">
-        <v>17001</v>
-      </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="1">
-        <f>B102*10+E102</f>
+        <f t="shared" si="2"/>
         <v>3004002</v>
       </c>
-      <c r="B102" s="8">
+      <c r="B102" s="7">
         <v>300400</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D102" s="10">
+      <c r="D102" s="9">
         <v>300400023</v>
       </c>
       <c r="E102" s="1">
@@ -4323,28 +4110,25 @@
       <c r="F102" s="1">
         <v>1000</v>
       </c>
-      <c r="G102" s="11" t="s">
+      <c r="G102" s="10" t="s">
         <v>88</v>
       </c>
       <c r="H102" s="1">
         <v>300</v>
       </c>
-      <c r="I102" s="1">
-        <v>17001</v>
-      </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="1">
-        <f>B103*10+E103</f>
+        <f t="shared" si="2"/>
         <v>3004003</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="7">
         <v>300400</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D103" s="10">
+      <c r="D103" s="9">
         <v>300400023</v>
       </c>
       <c r="E103" s="1">
@@ -4353,13 +4137,126 @@
       <c r="F103" s="1">
         <v>10000</v>
       </c>
-      <c r="G103" s="11" t="s">
+      <c r="G103" s="10" t="s">
         <v>88</v>
       </c>
       <c r="H103" s="1">
         <v>300</v>
       </c>
-      <c r="I103" s="1">
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="1">
+        <v>1039001</v>
+      </c>
+      <c r="B104" s="7">
+        <v>103900</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D104" s="9">
+        <v>103900001</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+      <c r="I104" s="1">
+        <v>17001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="1">
+        <v>1027001</v>
+      </c>
+      <c r="B105" s="7">
+        <v>102700</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D105" s="9">
+        <v>102700001</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1">
+        <v>17001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="1">
+        <v>1015001</v>
+      </c>
+      <c r="B106" s="7">
+        <v>101500</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D106" s="9">
+        <v>101500001</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1">
+        <v>17001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="1">
+        <v>1031001</v>
+      </c>
+      <c r="B107" s="7">
+        <v>103100</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D107" s="9">
+        <v>103100001</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1">
         <v>17001</v>
       </c>
     </row>

--- a/hall/resources/sample/runninglight.xlsx
+++ b/hall/resources/sample/runninglight.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -301,18 +301,6 @@
   </si>
   <si>
     <t>30_40_50_78</t>
-  </si>
-  <si>
-    <t>愤怒的小鸟</t>
-  </si>
-  <si>
-    <t>象财神</t>
-  </si>
-  <si>
-    <t>狼月</t>
-  </si>
-  <si>
-    <t>绿巨人</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.75" style="1" customWidth="1"/>
@@ -3955,7 +3943,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:8">
       <c r="A97" s="1">
         <f t="shared" si="2"/>
         <v>3001003</v>
@@ -3982,7 +3970,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <f t="shared" si="2"/>
         <v>3002001</v>
@@ -4009,7 +3997,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <f t="shared" si="2"/>
         <v>3002002</v>
@@ -4036,7 +4024,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <f t="shared" si="2"/>
         <v>3002003</v>
@@ -4063,7 +4051,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <f t="shared" si="2"/>
         <v>3004001</v>
@@ -4090,7 +4078,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <f t="shared" si="2"/>
         <v>3004002</v>
@@ -4117,7 +4105,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <f t="shared" si="2"/>
         <v>3004003</v>
@@ -4142,122 +4130,6 @@
       </c>
       <c r="H103" s="1">
         <v>300</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
-      <c r="A104" s="1">
-        <v>1039001</v>
-      </c>
-      <c r="B104" s="7">
-        <v>103900</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D104" s="9">
-        <v>103900001</v>
-      </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H104" s="1">
-        <v>0</v>
-      </c>
-      <c r="I104" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" s="1">
-        <v>1027001</v>
-      </c>
-      <c r="B105" s="7">
-        <v>102700</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D105" s="9">
-        <v>102700001</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H105" s="1">
-        <v>0</v>
-      </c>
-      <c r="I105" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9">
-      <c r="A106" s="1">
-        <v>1015001</v>
-      </c>
-      <c r="B106" s="7">
-        <v>101500</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D106" s="9">
-        <v>101500001</v>
-      </c>
-      <c r="E106" s="1">
-        <v>1</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H106" s="1">
-        <v>0</v>
-      </c>
-      <c r="I106" s="1">
-        <v>17001</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9">
-      <c r="A107" s="1">
-        <v>1031001</v>
-      </c>
-      <c r="B107" s="7">
-        <v>103100</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D107" s="9">
-        <v>103100001</v>
-      </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H107" s="1">
-        <v>0</v>
-      </c>
-      <c r="I107" s="1">
-        <v>17001</v>
       </c>
     </row>
   </sheetData>
